--- a/BD_MCAP.xlsx
+++ b/BD_MCAP.xlsx
@@ -17927,8 +17927,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="4b8b536fcb9f2c664ed0fa8e4c5bcaeb">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9c3fb262092b4aec5ef66bdd34acef6e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
     <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
     <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
     <xsd:element name="properties">
@@ -18136,23 +18136,19 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DBFF549-43CE-4B47-BA80-10A70B5A7091}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61744D0-81D7-4ABC-95E1-04F2DB0D56FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18161,4 +18157,8 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735DD5A6-4C2F-42DD-9205-630C8AB8EF63}"/>
 </file>
--- a/BD_MCAP.xlsx
+++ b/BD_MCAP.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/CicSFE_sp/Mercados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/BD_sp/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="612" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB81FD2-B9F1-4928-8B82-80EF5EF17C7B}"/>
@@ -1423,7 +1423,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal_Ipc_s" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -1760,7 +1760,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z44"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="3.85546875" style="35" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" style="35" customWidth="1"/>
@@ -2227,7 +2227,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:V261"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="42" customWidth="1"/>
     <col min="2" max="22" width="12.28515625" style="42" customWidth="1"/>
@@ -18128,15 +18128,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
@@ -18147,18 +18138,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61744D0-81D7-4ABC-95E1-04F2DB0D56FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61744D0-81D7-4ABC-95E1-04F2DB0D56FD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735DD5A6-4C2F-42DD-9205-630C8AB8EF63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735DD5A6-4C2F-42DD-9205-630C8AB8EF63}"/>
 </file>
--- a/BD_MCAP.xlsx
+++ b/BD_MCAP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/BD_sp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/CicSFE_sp/Mercados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="612" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB81FD2-B9F1-4928-8B82-80EF5EF17C7B}"/>
+  <xr:revisionPtr revIDLastSave="819" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A42CC2-922F-4E56-93C7-504F2E724E58}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -320,10 +320,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,6 +471,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -515,7 +523,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1111,8 +1119,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dashed">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
@@ -1120,8 +1139,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1421,12 +1441,25 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="5">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal_Ipc_s" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Per cent" xfId="4" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1760,7 +1793,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="3.85546875" style="35" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" style="35" customWidth="1"/>
@@ -1852,15 +1885,15 @@
         <v>76</v>
       </c>
       <c r="D12" s="139">
-        <v>45952</v>
+        <v>46163</v>
       </c>
       <c r="E12" s="139"/>
       <c r="F12" s="139" t="s">
         <v>75</v>
       </c>
       <c r="G12" s="139" t="str">
-        <f>"2025.09"</f>
-        <v>2025.09</v>
+        <f>"2026.04"</f>
+        <v>2026.04</v>
       </c>
       <c r="I12" s="137"/>
       <c r="J12" s="137"/>
@@ -2226,8 +2259,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V261"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:X261"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="42" customWidth="1"/>
     <col min="2" max="22" width="12.28515625" style="42" customWidth="1"/>
@@ -12136,7 +12169,7 @@
         <v>262478.17684078281</v>
       </c>
     </row>
-    <row r="177" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>2023.12</v>
       </c>
@@ -12204,7 +12237,7 @@
         <v>329778.4758091601</v>
       </c>
     </row>
-    <row r="178" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>2024.01</v>
       </c>
@@ -12272,7 +12305,7 @@
         <v>444891.87732220639</v>
       </c>
     </row>
-    <row r="179" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>2024.02</v>
       </c>
@@ -12340,7 +12373,7 @@
         <v>421877.03609497129</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>2024.03</v>
       </c>
@@ -12408,7 +12441,7 @@
         <v>504512.15643104317</v>
       </c>
     </row>
-    <row r="181" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>2024.04</v>
       </c>
@@ -12476,7 +12509,7 @@
         <v>738973.61274585431</v>
       </c>
     </row>
-    <row r="182" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>2024.05</v>
       </c>
@@ -12544,7 +12577,7 @@
         <v>729161.75943937025</v>
       </c>
     </row>
-    <row r="183" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>2024.06</v>
       </c>
@@ -12612,7 +12645,7 @@
         <v>729448.00756812969</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>2024.07</v>
       </c>
@@ -12680,7 +12713,7 @@
         <v>1085575.031158292</v>
       </c>
     </row>
-    <row r="185" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>2024.08</v>
       </c>
@@ -12748,7 +12781,7 @@
         <v>829456.87572663266</v>
       </c>
     </row>
-    <row r="186" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>2024.09</v>
       </c>
@@ -12816,7 +12849,7 @@
         <v>850953.44805030979</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>2024.1</v>
       </c>
@@ -12884,7 +12917,7 @@
         <v>966704.41150283674</v>
       </c>
     </row>
-    <row r="188" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>2024.11</v>
       </c>
@@ -12952,7 +12985,7 @@
         <v>868031.1167032473</v>
       </c>
     </row>
-    <row r="189" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>2024.12</v>
       </c>
@@ -13019,8 +13052,9 @@
       <c r="V189" s="69">
         <v>842923.57459634007</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W189" s="144"/>
+    </row>
+    <row r="190" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>2025.01</v>
       </c>
@@ -13088,7 +13122,7 @@
         <v>783986.56366171606</v>
       </c>
     </row>
-    <row r="191" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>2025.02</v>
       </c>
@@ -13156,7 +13190,7 @@
         <v>792572</v>
       </c>
     </row>
-    <row r="192" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>2025.03</v>
       </c>
@@ -13224,7 +13258,7 @@
         <v>952577</v>
       </c>
     </row>
-    <row r="193" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>2025.04</v>
       </c>
@@ -13292,7 +13326,7 @@
         <v>1149859</v>
       </c>
     </row>
-    <row r="194" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>2025.05</v>
       </c>
@@ -13360,7 +13394,7 @@
         <v>865866</v>
       </c>
     </row>
-    <row r="195" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>2025.06</v>
       </c>
@@ -13428,7 +13462,7 @@
         <v>981248</v>
       </c>
     </row>
-    <row r="196" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>2025.07</v>
       </c>
@@ -13496,7 +13530,7 @@
         <v>957231</v>
       </c>
     </row>
-    <row r="197" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>2025.08</v>
       </c>
@@ -13564,7 +13598,7 @@
         <v>1204196</v>
       </c>
     </row>
-    <row r="198" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>2025.09</v>
       </c>
@@ -13589,8 +13623,8 @@
       <c r="H198" s="10">
         <v>36059</v>
       </c>
-      <c r="I198" s="25" t="e">
-        <v>#N/A</v>
+      <c r="I198" s="25">
+        <v>2169458</v>
       </c>
       <c r="J198" s="99">
         <v>9</v>
@@ -13632,483 +13666,486 @@
         <v>1182902</v>
       </c>
     </row>
-    <row r="199" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>2025.1</v>
       </c>
-      <c r="B199" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I199" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J199" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K199" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L199" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M199" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N199" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O199" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P199" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q199" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R199" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S199" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T199" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U199" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V199" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="200" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B199" s="73">
+        <v>4250</v>
+      </c>
+      <c r="C199" s="10">
+        <v>211136</v>
+      </c>
+      <c r="D199" s="10">
+        <v>2926332</v>
+      </c>
+      <c r="E199" s="10">
+        <v>913038</v>
+      </c>
+      <c r="F199" s="10">
+        <v>969338</v>
+      </c>
+      <c r="G199" s="10">
+        <v>4313</v>
+      </c>
+      <c r="H199" s="10">
+        <v>38383</v>
+      </c>
+      <c r="I199" s="25">
+        <v>5066791</v>
+      </c>
+      <c r="J199" s="99">
+        <v>11</v>
+      </c>
+      <c r="K199" s="10">
+        <v>29</v>
+      </c>
+      <c r="L199" s="25">
+        <v>10000000</v>
+      </c>
+      <c r="M199" s="28">
+        <v>787</v>
+      </c>
+      <c r="N199" s="18">
+        <v>57</v>
+      </c>
+      <c r="O199" s="94">
+        <v>9</v>
+      </c>
+      <c r="P199" s="70">
+        <v>30497</v>
+      </c>
+      <c r="Q199" s="71">
+        <v>6531</v>
+      </c>
+      <c r="R199" s="71">
+        <v>252081</v>
+      </c>
+      <c r="S199" s="71">
+        <v>132708</v>
+      </c>
+      <c r="T199" s="71">
+        <v>969338</v>
+      </c>
+      <c r="U199" s="72">
+        <v>38383</v>
+      </c>
+      <c r="V199" s="69">
+        <v>1429539</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>2025.11</v>
       </c>
-      <c r="B200" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I200" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J200" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K200" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L200" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M200" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N200" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O200" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P200" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q200" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R200" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S200" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T200" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U200" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V200" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="201" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B200" s="141">
+        <v>0</v>
+      </c>
+      <c r="C200" s="142">
+        <v>372911</v>
+      </c>
+      <c r="D200" s="142">
+        <v>4440371</v>
+      </c>
+      <c r="E200" s="142">
+        <v>1003733</v>
+      </c>
+      <c r="F200" s="142">
+        <v>1080928</v>
+      </c>
+      <c r="G200" s="142">
+        <v>0</v>
+      </c>
+      <c r="H200" s="143">
+        <v>36658</v>
+      </c>
+      <c r="I200" s="25">
+        <v>6934602</v>
+      </c>
+      <c r="J200" s="99">
+        <v>16</v>
+      </c>
+      <c r="K200" s="10">
+        <v>27</v>
+      </c>
+      <c r="L200" s="25">
+        <v>0</v>
+      </c>
+      <c r="M200" s="28">
+        <v>667</v>
+      </c>
+      <c r="N200" s="18">
+        <v>43.4</v>
+      </c>
+      <c r="O200" s="94">
+        <v>9</v>
+      </c>
+      <c r="P200" s="70">
+        <v>14403</v>
+      </c>
+      <c r="Q200" s="71">
+        <v>13824</v>
+      </c>
+      <c r="R200" s="71">
+        <v>286093</v>
+      </c>
+      <c r="S200" s="71">
+        <v>138770</v>
+      </c>
+      <c r="T200" s="71">
+        <v>1080928</v>
+      </c>
+      <c r="U200" s="72">
+        <v>36658</v>
+      </c>
+      <c r="V200" s="69">
+        <v>1570676</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>2025.12</v>
       </c>
-      <c r="B201" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I201" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J201" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K201" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L201" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M201" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N201" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O201" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P201" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q201" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R201" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S201" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T201" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U201" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V201" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="202" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B201" s="141">
+        <v>77906</v>
+      </c>
+      <c r="C201" s="142">
+        <v>198507</v>
+      </c>
+      <c r="D201" s="10">
+        <v>1948491</v>
+      </c>
+      <c r="E201" s="142">
+        <v>988084</v>
+      </c>
+      <c r="F201" s="142">
+        <v>1312247</v>
+      </c>
+      <c r="G201" s="10">
+        <v>0</v>
+      </c>
+      <c r="H201" s="143">
+        <v>44014</v>
+      </c>
+      <c r="I201" s="25">
+        <v>4569249</v>
+      </c>
+      <c r="J201" s="99">
+        <v>16</v>
+      </c>
+      <c r="K201" s="10">
+        <v>40</v>
+      </c>
+      <c r="L201" s="25">
+        <v>162302724</v>
+      </c>
+      <c r="M201" s="28">
+        <v>686</v>
+      </c>
+      <c r="N201" s="18">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="O201" s="94">
+        <v>8.9</v>
+      </c>
+      <c r="P201" s="70">
+        <v>18956</v>
+      </c>
+      <c r="Q201" s="71">
+        <v>30812</v>
+      </c>
+      <c r="R201" s="71">
+        <v>313894</v>
+      </c>
+      <c r="S201" s="71">
+        <v>135859</v>
+      </c>
+      <c r="T201" s="71">
+        <v>1312247</v>
+      </c>
+      <c r="U201" s="72">
+        <v>44014</v>
+      </c>
+      <c r="V201" s="69">
+        <v>1855783</v>
+      </c>
+      <c r="W201" s="144"/>
+      <c r="X201" s="145"/>
+    </row>
+    <row r="202" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>2026.01</v>
       </c>
-      <c r="B202" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I202" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J202" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K202" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L202" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M202" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N202" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O202" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P202" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q202" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R202" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S202" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T202" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U202" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V202" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="203" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B202" s="73">
+        <v>0</v>
+      </c>
+      <c r="C202" s="10">
+        <v>210556</v>
+      </c>
+      <c r="D202" s="10">
+        <v>3540310</v>
+      </c>
+      <c r="E202" s="10">
+        <v>821845</v>
+      </c>
+      <c r="F202" s="10">
+        <v>697490</v>
+      </c>
+      <c r="G202" s="10">
+        <v>0</v>
+      </c>
+      <c r="H202" s="10">
+        <v>45846</v>
+      </c>
+      <c r="I202" s="25">
+        <v>5586047</v>
+      </c>
+      <c r="J202" s="99">
+        <v>10</v>
+      </c>
+      <c r="K202" s="10">
+        <v>19</v>
+      </c>
+      <c r="L202" s="25">
+        <v>0</v>
+      </c>
+      <c r="M202" s="28">
+        <v>757</v>
+      </c>
+      <c r="N202" s="18">
+        <v>36.9</v>
+      </c>
+      <c r="O202" s="94">
+        <v>7</v>
+      </c>
+      <c r="P202" s="70">
+        <v>147250</v>
+      </c>
+      <c r="Q202" s="71">
+        <v>2883</v>
+      </c>
+      <c r="R202" s="71">
+        <v>272335</v>
+      </c>
+      <c r="S202" s="71">
+        <v>151028</v>
+      </c>
+      <c r="T202" s="71">
+        <v>967490</v>
+      </c>
+      <c r="U202" s="72">
+        <v>45846</v>
+      </c>
+      <c r="V202" s="69">
+        <v>1586833</v>
+      </c>
+    </row>
+    <row r="203" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>2026.02</v>
       </c>
-      <c r="B203" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I203" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J203" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K203" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L203" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M203" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N203" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O203" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P203" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q203" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R203" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S203" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T203" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U203" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V203" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="204" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B203" s="73">
+        <v>0</v>
+      </c>
+      <c r="C203" s="10">
+        <v>191296</v>
+      </c>
+      <c r="D203" s="10">
+        <v>1472109</v>
+      </c>
+      <c r="E203" s="10">
+        <v>870353</v>
+      </c>
+      <c r="F203" s="10">
+        <v>1071527</v>
+      </c>
+      <c r="G203" s="10">
+        <v>0</v>
+      </c>
+      <c r="H203" s="10">
+        <v>50748</v>
+      </c>
+      <c r="I203" s="25">
+        <v>3656034</v>
+      </c>
+      <c r="J203" s="99">
+        <v>8</v>
+      </c>
+      <c r="K203" s="10">
+        <v>29</v>
+      </c>
+      <c r="L203" s="25">
+        <v>0</v>
+      </c>
+      <c r="M203" s="28">
+        <v>777</v>
+      </c>
+      <c r="N203" s="18">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="O203" s="94">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="P203" s="70">
+        <v>5330</v>
+      </c>
+      <c r="Q203" s="71">
+        <v>6231</v>
+      </c>
+      <c r="R203" s="71">
+        <v>243034</v>
+      </c>
+      <c r="S203" s="71">
+        <v>113006</v>
+      </c>
+      <c r="T203" s="71">
+        <v>1071527</v>
+      </c>
+      <c r="U203" s="72">
+        <v>50748</v>
+      </c>
+      <c r="V203" s="69">
+        <v>1489876</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>2026.03</v>
       </c>
-      <c r="B204" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I204" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J204" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K204" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L204" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M204" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N204" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O204" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P204" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q204" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R204" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S204" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T204" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U204" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V204" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="205" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B204" s="73">
+        <v>0</v>
+      </c>
+      <c r="C204" s="10">
+        <v>194992</v>
+      </c>
+      <c r="D204" s="10">
+        <v>649267</v>
+      </c>
+      <c r="E204" s="10">
+        <v>1027209</v>
+      </c>
+      <c r="F204" s="10">
+        <v>1188176</v>
+      </c>
+      <c r="G204" s="10">
+        <v>6343</v>
+      </c>
+      <c r="H204" s="10">
+        <v>61454</v>
+      </c>
+      <c r="I204" s="25">
+        <v>3127441</v>
+      </c>
+      <c r="J204" s="99">
+        <v>9</v>
+      </c>
+      <c r="K204" s="10">
+        <v>30</v>
+      </c>
+      <c r="L204" s="25">
+        <v>0</v>
+      </c>
+      <c r="M204" s="28">
+        <v>995</v>
+      </c>
+      <c r="N204" s="18">
+        <v>34.1</v>
+      </c>
+      <c r="O204" s="94">
+        <v>7.4</v>
+      </c>
+      <c r="P204" s="70">
+        <v>31321</v>
+      </c>
+      <c r="Q204" s="71">
+        <v>13208</v>
+      </c>
+      <c r="R204" s="71">
+        <v>328807</v>
+      </c>
+      <c r="S204" s="71">
+        <v>137421</v>
+      </c>
+      <c r="T204" s="71">
+        <v>1188176</v>
+      </c>
+      <c r="U204" s="72">
+        <v>61454</v>
+      </c>
+      <c r="V204" s="69">
+        <v>1760388</v>
+      </c>
+    </row>
+    <row r="205" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>2026.04</v>
       </c>
-      <c r="B205" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I205" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J205" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K205" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L205" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M205" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N205" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O205" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P205" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q205" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R205" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S205" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T205" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U205" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V205" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="206" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B205" s="73">
+        <v>0</v>
+      </c>
+      <c r="C205" s="10">
+        <v>335761</v>
+      </c>
+      <c r="D205" s="10">
+        <v>2304115</v>
+      </c>
+      <c r="E205" s="10">
+        <v>1021817</v>
+      </c>
+      <c r="F205" s="10">
+        <v>988786</v>
+      </c>
+      <c r="G205" s="10">
+        <v>411173</v>
+      </c>
+      <c r="H205" s="10">
+        <v>58144</v>
+      </c>
+      <c r="I205" s="25">
+        <v>5119796</v>
+      </c>
+      <c r="J205" s="99">
+        <v>15</v>
+      </c>
+      <c r="K205" s="10">
+        <v>22</v>
+      </c>
+      <c r="L205" s="25">
+        <v>0</v>
+      </c>
+      <c r="M205" s="28">
+        <v>1035</v>
+      </c>
+      <c r="N205" s="18">
+        <v>30.4</v>
+      </c>
+      <c r="O205" s="94">
+        <v>6.8</v>
+      </c>
+      <c r="P205" s="70">
+        <v>34962</v>
+      </c>
+      <c r="Q205" s="71">
+        <v>22863</v>
+      </c>
+      <c r="R205" s="71">
+        <v>287194</v>
+      </c>
+      <c r="S205" s="71">
+        <v>154784</v>
+      </c>
+      <c r="T205" s="71">
+        <v>988786</v>
+      </c>
+      <c r="U205" s="72">
+        <v>58144</v>
+      </c>
+      <c r="V205" s="69">
+        <v>1546733</v>
+      </c>
+      <c r="W205" s="146"/>
+    </row>
+    <row r="206" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>2026.05</v>
       </c>
@@ -14176,7 +14213,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="207" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>2026.06</v>
       </c>
@@ -14244,7 +14281,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="208" spans="1:22" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>2026.07</v>
       </c>
@@ -17927,6 +17964,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
     <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
@@ -18127,17 +18175,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -18148,7 +18185,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A61744D0-81D7-4ABC-95E1-04F2DB0D56FD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A87D32-22F8-4B25-9692-D498E7E5A8B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5391394E-ACC2-484F-B6D4-A29C0AE8D23F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -18166,17 +18214,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{735DD5A6-4C2F-42DD-9205-630C8AB8EF63}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
   <ds:schemaRefs>

--- a/BD_MCAP.xlsx
+++ b/BD_MCAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/CicSFE_sp/Mercados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/BD_sp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="819" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84A42CC2-922F-4E56-93C7-504F2E724E58}"/>
+  <xr:revisionPtr revIDLastSave="842" documentId="13_ncr:1_{C2533B98-536A-43E9-9ACC-FF3779DD6A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BF6C5BD-F8BB-483F-A2D1-4BC0D01B5640}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="2" r:id="rId1"/>
@@ -1885,15 +1885,15 @@
         <v>76</v>
       </c>
       <c r="D12" s="139">
-        <v>46163</v>
+        <v>46197</v>
       </c>
       <c r="E12" s="139"/>
       <c r="F12" s="139" t="s">
         <v>75</v>
       </c>
       <c r="G12" s="139" t="str">
-        <f>"2026.04"</f>
-        <v>2026.04</v>
+        <f>"2026.05"</f>
+        <v>2026.05</v>
       </c>
       <c r="I12" s="137"/>
       <c r="J12" s="137"/>
@@ -14149,68 +14149,68 @@
       <c r="A206" s="1">
         <v>2026.05</v>
       </c>
-      <c r="B206" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I206" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J206" s="99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K206" s="10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L206" s="25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M206" s="28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N206" s="18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O206" s="94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P206" s="70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q206" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R206" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S206" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T206" s="71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U206" s="72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V206" s="69" t="e">
-        <v>#N/A</v>
+      <c r="B206" s="73">
+        <v>0</v>
+      </c>
+      <c r="C206" s="10">
+        <v>235189</v>
+      </c>
+      <c r="D206" s="10">
+        <v>2742383</v>
+      </c>
+      <c r="E206" s="10">
+        <v>1032087</v>
+      </c>
+      <c r="F206" s="10">
+        <v>1207662</v>
+      </c>
+      <c r="G206" s="10">
+        <v>0</v>
+      </c>
+      <c r="H206" s="10">
+        <v>53040</v>
+      </c>
+      <c r="I206" s="25">
+        <v>5270362</v>
+      </c>
+      <c r="J206" s="99">
+        <v>9</v>
+      </c>
+      <c r="K206" s="10">
+        <v>37</v>
+      </c>
+      <c r="L206" s="25">
+        <v>0</v>
+      </c>
+      <c r="M206" s="28">
+        <v>889</v>
+      </c>
+      <c r="N206" s="18">
+        <v>28.2</v>
+      </c>
+      <c r="O206" s="94">
+        <v>6.9</v>
+      </c>
+      <c r="P206" s="70">
+        <v>42941</v>
+      </c>
+      <c r="Q206" s="71">
+        <v>29549</v>
+      </c>
+      <c r="R206" s="71">
+        <v>274550</v>
+      </c>
+      <c r="S206" s="71">
+        <v>152493</v>
+      </c>
+      <c r="T206" s="71">
+        <v>1207662</v>
+      </c>
+      <c r="U206" s="72">
+        <v>53040</v>
+      </c>
+      <c r="V206" s="69">
+        <v>1760235</v>
       </c>
     </row>
     <row r="207" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -17975,6 +17975,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
     <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
@@ -18175,15 +18184,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1A87D32-22F8-4B25-9692-D498E7E5A8B0}">
   <ds:schemaRefs>
@@ -18196,6 +18196,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5391394E-ACC2-484F-B6D4-A29C0AE8D23F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18212,12 +18220,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7A1AE2-79B5-45E2-9D53-11A870F1D987}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>